--- a/scripts/ground-truth/judah-2026-04-25.xlsx
+++ b/scripts/ground-truth/judah-2026-04-25.xlsx
@@ -1,28 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
-  <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5D7A801B-D917-40D4-93CB-57F94FFC765B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" firstSheet="2" activeTab="3"/>
   </bookViews>
   <sheets>
-    <sheet name="README" sheetId="1" r:id="rId1"/>
-    <sheet name="Metadata" sheetId="2" r:id="rId2"/>
-    <sheet name="Goals" sheetId="3" r:id="rId3"/>
-    <sheet name="Saves" sheetId="4" r:id="rId4"/>
-    <sheet name="Distribution" sheetId="5" r:id="rId5"/>
-    <sheet name="Crosses" sheetId="6" r:id="rId6"/>
-    <sheet name="Sweeper" sheetId="7" r:id="rId7"/>
-    <sheet name="1v1s" sheetId="8" r:id="rId8"/>
+    <sheet sheetId="1" name="README" state="visible" r:id="rId4"/>
+    <sheet sheetId="2" name="Metadata" state="visible" r:id="rId5"/>
+    <sheet sheetId="3" name="Goals" state="visible" r:id="rId6"/>
+    <sheet sheetId="4" name="Saves" state="visible" r:id="rId7"/>
+    <sheet sheetId="5" name="Distribution" state="visible" r:id="rId8"/>
+    <sheet sheetId="6" name="Crosses" state="visible" r:id="rId9"/>
+    <sheet sheetId="7" name="Sweeper" state="visible" r:id="rId10"/>
+    <sheet sheetId="8" name="1v1s" state="visible" r:id="rId11"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="230">
   <si>
     <t>STIX Match Ground-Truth Tagger</t>
   </si>
@@ -198,6 +197,9 @@
     <t>video_job_id</t>
   </si>
   <si>
+    <t>60cfa445-6364-4147-9830-0d1ddeffcb37</t>
+  </si>
+  <si>
     <t>Fill in after upload — needed for eval</t>
   </si>
   <si>
@@ -231,6 +233,75 @@
     <t>GK observations</t>
   </si>
   <si>
+    <t>4:05</t>
+  </si>
+  <si>
+    <t>Us</t>
+  </si>
+  <si>
+    <t>Open play</t>
+  </si>
+  <si>
+    <t>Tap-in</t>
+  </si>
+  <si>
+    <t>6-Yard Box</t>
+  </si>
+  <si>
+    <t>Low</t>
+  </si>
+  <si>
+    <t>Centre</t>
+  </si>
+  <si>
+    <t>Black player drives into 6 yard box. GK comes out for 1v1, ball bounces off of him and onto the feet of the goal scorer</t>
+  </si>
+  <si>
+    <t>GK was brave and came out for 1v1. Rebound to opposing player for an easy tap in.</t>
+  </si>
+  <si>
+    <t>9:34</t>
+  </si>
+  <si>
+    <t>Right-wing dribble to byline, square pass across goal, central tap-in. Opp GK moved to near post, ball went central.</t>
+  </si>
+  <si>
+    <t>12:24</t>
+  </si>
+  <si>
+    <t>Winger runs right side, low pass to striker, opp intercepts then poor pass into the 6-yard box where the winger had made a run. Easy tap-in to middle. GK on the post, didn't move fast enough.</t>
+  </si>
+  <si>
+    <t>40:14</t>
+  </si>
+  <si>
+    <t>Driven</t>
+  </si>
+  <si>
+    <t>Right Channel</t>
+  </si>
+  <si>
+    <t>Mid</t>
+  </si>
+  <si>
+    <t>GK Right</t>
+  </si>
+  <si>
+    <t>Ball played in from sideline to centre, player turns and runs through the middle channel, shot from outside the box right channel, low left corner. GK set tight to post, beaten cleanly.</t>
+  </si>
+  <si>
+    <t>49:19</t>
+  </si>
+  <si>
+    <t>Central Box</t>
+  </si>
+  <si>
+    <t>Ball played in from the right side to center mid who takes the ball to just outside the 6-yard (on the left) and drives the ball against the grain into the GK goal left</t>
+  </si>
+  <si>
+    <t>GK tracked the player but lost the angle in goal leaving the left side of the goal open. Wasn't set and couldn't push back the opposite direction</t>
+  </si>
+  <si>
     <t>Shot origin</t>
   </si>
   <si>
@@ -249,6 +320,168 @@
     <t>Body zone (A/B/C)</t>
   </si>
   <si>
+    <t>10:11</t>
+  </si>
+  <si>
+    <t>Central Distance</t>
+  </si>
+  <si>
+    <t>Foot</t>
+  </si>
+  <si>
+    <t>Yes</t>
+  </si>
+  <si>
+    <t>Smother</t>
+  </si>
+  <si>
+    <t>Held</t>
+  </si>
+  <si>
+    <t>B</t>
+  </si>
+  <si>
+    <t>GK Left</t>
+  </si>
+  <si>
+    <t>giveaway by defender, small toe poke slow rolls into the box</t>
+  </si>
+  <si>
+    <t>GK ready and comes out to smother the ball low and take all options away from the striker</t>
+  </si>
+  <si>
+    <t>10:27</t>
+  </si>
+  <si>
+    <t>Wide Right</t>
+  </si>
+  <si>
+    <t>Parry</t>
+  </si>
+  <si>
+    <t>Corner</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t xml:space="preserve">winger wins the ball and drives a low hard shot far post. </t>
+  </si>
+  <si>
+    <t>GK set, power step to the right, drive hands along the ground to tip the ball wide. Hit the post.</t>
+  </si>
+  <si>
+    <t>14:37</t>
+  </si>
+  <si>
+    <t>Catch</t>
+  </si>
+  <si>
+    <t>A</t>
+  </si>
+  <si>
+    <t>GK gives ball away to winger who then hits the ball first time low at the GKs feet</t>
+  </si>
+  <si>
+    <t>After the giveaway, GK finds their angle, gets set on the toes and collects the ball with a successful scoop</t>
+  </si>
+  <si>
+    <t>17:43</t>
+  </si>
+  <si>
+    <t>K-Barrier</t>
+  </si>
+  <si>
+    <t>Rebound (safe)</t>
+  </si>
+  <si>
+    <t>Winger battles through a mele of players to get an in close shot on the GK</t>
+  </si>
+  <si>
+    <t>GK prepared, steps off the line to make the low block</t>
+  </si>
+  <si>
+    <t>23:18</t>
+  </si>
+  <si>
+    <t>Center mid receives a ball in open play from the winger outside of the 6-yard back. Takes a low driven shot to the right.</t>
+  </si>
+  <si>
+    <t>GK standing a bit left in the goal, but is set and pushes hard through a power step and reaches to parry the ball wide for a corner.</t>
+  </si>
+  <si>
+    <t>24:47</t>
+  </si>
+  <si>
+    <t>Center mid turns after a pass outside of the 6-yard box. Dives the ball mid height to the GK right</t>
+  </si>
+  <si>
+    <t>GK is set but standing a bit too far left, is ready for the shot, parry the ball from mid height wide for a corner</t>
+  </si>
+  <si>
+    <t>25:14</t>
+  </si>
+  <si>
+    <t>Corner Left</t>
+  </si>
+  <si>
+    <t>Corner kick delivered into the GK arms</t>
+  </si>
+  <si>
+    <t>GK on the near post during the corner, set, and makes a calm save</t>
+  </si>
+  <si>
+    <t>25:42</t>
+  </si>
+  <si>
+    <t>No</t>
+  </si>
+  <si>
+    <t>Winger drives the ball at goal but off target</t>
+  </si>
+  <si>
+    <t>GK parry the shot going wide to be safe, resulting in a corner.</t>
+  </si>
+  <si>
+    <t>37:25</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Header driven towards the net off a corner to the low corner</t>
+  </si>
+  <si>
+    <t>GK was moving from right to left after the corner, dives back the other way to save the ball and hold on.</t>
+  </si>
+  <si>
+    <t>45:56</t>
+  </si>
+  <si>
+    <t>Rebound (dangerous)</t>
+  </si>
+  <si>
+    <t>Opposing midfielder drives the ball through the middle beating several players but GK blocks the ball</t>
+  </si>
+  <si>
+    <t>GK started on left post, but challenged in the middle in time to make the block and save</t>
+  </si>
+  <si>
+    <t>49:00</t>
+  </si>
+  <si>
+    <t>Unclear</t>
+  </si>
+  <si>
+    <t>Top</t>
+  </si>
+  <si>
+    <t>bouncing ball in from a cross, didn't get good enough contact</t>
+  </si>
+  <si>
+    <t>GK bobbles the bouncing ball but is able to recover.</t>
+  </si>
+  <si>
     <t>QUICK TOTALS — fill these IN PLACE OF logging every event if you do not want to tag row-by-row.</t>
   </si>
   <si>
@@ -309,6 +542,153 @@
     <t>First touch</t>
   </si>
   <si>
+    <t>9:20</t>
+  </si>
+  <si>
+    <t>Goal kick</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Short to defender</t>
+  </si>
+  <si>
+    <t>Right</t>
+  </si>
+  <si>
+    <t>Defender</t>
+  </si>
+  <si>
+    <t>Unable to see the first touch, pass successful to the center mid</t>
+  </si>
+  <si>
+    <t>10:15</t>
+  </si>
+  <si>
+    <t>After save</t>
+  </si>
+  <si>
+    <t>Throw</t>
+  </si>
+  <si>
+    <t>Left</t>
+  </si>
+  <si>
+    <t>Clean</t>
+  </si>
+  <si>
+    <t>Short pass to the left back who was under pressure, couldn't gone across the the right back but turns and plays it to the winger in support</t>
+  </si>
+  <si>
+    <t>11:30</t>
+  </si>
+  <si>
+    <t>Loose ball in box</t>
+  </si>
+  <si>
+    <t>Drop-kick</t>
+  </si>
+  <si>
+    <t>Long to forward</t>
+  </si>
+  <si>
+    <t>Midfielder</t>
+  </si>
+  <si>
+    <t>Long ball from drop kick goes out of bounds on the opposing sideline</t>
+  </si>
+  <si>
+    <t>13:26</t>
+  </si>
+  <si>
+    <t>Backpass</t>
+  </si>
+  <si>
+    <t>Sideways across back</t>
+  </si>
+  <si>
+    <t>Mishit</t>
+  </si>
+  <si>
+    <t>Backpass goes to GK who fumbles the pass, is intercepted, but recovered by the GK in the 6-yard box</t>
+  </si>
+  <si>
+    <t>13:56</t>
+  </si>
+  <si>
+    <t>Drop kick up the middle, touched by midfield who turns and finds a teammate</t>
+  </si>
+  <si>
+    <t>14:33</t>
+  </si>
+  <si>
+    <t>Defender gives a little touch back to the GK who was not ready. Giveaway to winger resulting in a shot.</t>
+  </si>
+  <si>
+    <t>14:41</t>
+  </si>
+  <si>
+    <t>Defender sees pressure from the opposing winger who is pressing and makes a calm pass to his supporting winger</t>
+  </si>
+  <si>
+    <t>22:03</t>
+  </si>
+  <si>
+    <t>24:34</t>
+  </si>
+  <si>
+    <t>25:15</t>
+  </si>
+  <si>
+    <t>Forward</t>
+  </si>
+  <si>
+    <t>Long drop kick bounces off an opposing player leading to our possession outside of the 6-yard box</t>
+  </si>
+  <si>
+    <t>34:24</t>
+  </si>
+  <si>
+    <t>34:44</t>
+  </si>
+  <si>
+    <t>Left back cuts the ball back to switch play and ball moved up into the midfield.</t>
+  </si>
+  <si>
+    <t>37:27</t>
+  </si>
+  <si>
+    <t>37:51</t>
+  </si>
+  <si>
+    <t>Heavy</t>
+  </si>
+  <si>
+    <t>41:23</t>
+  </si>
+  <si>
+    <t>No touch, ball went to the end line and other GK got the first touch</t>
+  </si>
+  <si>
+    <t>44:05</t>
+  </si>
+  <si>
+    <t>Defender holds ball too long and kicks it off the pressing striker</t>
+  </si>
+  <si>
+    <t>44:28</t>
+  </si>
+  <si>
+    <t>Defender pressured from the winger and makes a pass out to his midfielder to push up the field</t>
+  </si>
+  <si>
+    <t>46:55</t>
+  </si>
+  <si>
+    <t>49:02</t>
+  </si>
+  <si>
     <t>Side</t>
   </si>
   <si>
@@ -331,397 +711,19 @@
   </si>
   <si>
     <t>Event type</t>
-  </si>
-  <si>
-    <t>4:05</t>
-  </si>
-  <si>
-    <t>Us</t>
-  </si>
-  <si>
-    <t>Open play</t>
-  </si>
-  <si>
-    <t>Tap-in</t>
-  </si>
-  <si>
-    <t>6-Yard Box</t>
-  </si>
-  <si>
-    <t>Low</t>
-  </si>
-  <si>
-    <t>Centre</t>
-  </si>
-  <si>
-    <t>Black player drives into 6 yard box. GK comes out for 1v1, ball bounces off of him and onto the feet of the goal scorer</t>
-  </si>
-  <si>
-    <t>GK was brave and came out for 1v1. Rebound to opposing player for an easy tap in.</t>
-  </si>
-  <si>
-    <t>9:34</t>
-  </si>
-  <si>
-    <t>12:24</t>
-  </si>
-  <si>
-    <t>Winger runs right side, low pass to striker, opp intercepts then poor pass into the 6-yard box where the winger had made a run. Easy tap-in to middle. GK on the post, didn't move fast enough.</t>
-  </si>
-  <si>
-    <t>Right-wing dribble to byline, square pass across goal, central tap-in. Opp GK moved to near post, ball went central.</t>
-  </si>
-  <si>
-    <t>Ball played in from sideline to centre, player turns and runs through the middle channel, shot from outside the box right channel, low left corner. GK set tight to post, beaten cleanly.</t>
-  </si>
-  <si>
-    <t>49:19</t>
-  </si>
-  <si>
-    <t>9:20</t>
-  </si>
-  <si>
-    <t>Goal kick</t>
-  </si>
-  <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>Yes</t>
-  </si>
-  <si>
-    <t>No</t>
-  </si>
-  <si>
-    <t>Short to defender</t>
-  </si>
-  <si>
-    <t>Right</t>
-  </si>
-  <si>
-    <t>Defender</t>
-  </si>
-  <si>
-    <t>Unable to see the first touch, pass successful to the center mid</t>
-  </si>
-  <si>
-    <t>10:11</t>
-  </si>
-  <si>
-    <t>Central Distance</t>
-  </si>
-  <si>
-    <t>Foot</t>
-  </si>
-  <si>
-    <t>Smother</t>
-  </si>
-  <si>
-    <t>Held</t>
-  </si>
-  <si>
-    <t>B</t>
-  </si>
-  <si>
-    <t>GK Left</t>
-  </si>
-  <si>
-    <t>giveaway by defender, small toe poke slow rolls into the box</t>
-  </si>
-  <si>
-    <t>GK ready and comes out to smother the ball low and take all options away from the striker</t>
-  </si>
-  <si>
-    <t>10:15</t>
-  </si>
-  <si>
-    <t>After save</t>
-  </si>
-  <si>
-    <t>Throw</t>
-  </si>
-  <si>
-    <t>Left</t>
-  </si>
-  <si>
-    <t>Clean</t>
-  </si>
-  <si>
-    <t>Short pass to the left back who was under pressure, couldn't gone across the the right back but turns and plays it to the winger in support</t>
-  </si>
-  <si>
-    <t>10:27</t>
-  </si>
-  <si>
-    <t>Wide Right</t>
-  </si>
-  <si>
-    <t>Parry</t>
-  </si>
-  <si>
-    <t>Corner</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>GK Right</t>
-  </si>
-  <si>
-    <t xml:space="preserve">winger wins the ball and drives a low hard shot far post. </t>
-  </si>
-  <si>
-    <t>GK set, power step to the right, drive hands along the ground to tip the ball wide. Hit the post.</t>
-  </si>
-  <si>
-    <t>11:30</t>
-  </si>
-  <si>
-    <t>Loose ball in box</t>
-  </si>
-  <si>
-    <t>Drop-kick</t>
-  </si>
-  <si>
-    <t>Long to forward</t>
-  </si>
-  <si>
-    <t>Midfielder</t>
-  </si>
-  <si>
-    <t>Mishit</t>
-  </si>
-  <si>
-    <t>Long ball from drop kick goes out of bounds on the opposing sideline</t>
-  </si>
-  <si>
-    <t>13:26</t>
-  </si>
-  <si>
-    <t>Backpass</t>
-  </si>
-  <si>
-    <t>Sideways across back</t>
-  </si>
-  <si>
-    <t>Backpass goes to GK who fumbles the pass, is intercepted, but recovered by the GK in the 6-yard box</t>
-  </si>
-  <si>
-    <t>13:56</t>
-  </si>
-  <si>
-    <t>Drop kick up the middle, touched by midfield who turns and finds a teammate</t>
-  </si>
-  <si>
-    <t>14:33</t>
-  </si>
-  <si>
-    <t>Defender gives a little touch back to the GK who was not ready. Giveaway to winger resulting in a shot.</t>
-  </si>
-  <si>
-    <t>14:37</t>
-  </si>
-  <si>
-    <t>Right Channel</t>
-  </si>
-  <si>
-    <t>Catch</t>
-  </si>
-  <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>GK gives ball away to winger who then hits the ball first time low at the GKs feet</t>
-  </si>
-  <si>
-    <t>After the giveaway, GK finds their angle, gets set on the toes and collects the ball with a successful scoop</t>
-  </si>
-  <si>
-    <t>14:41</t>
-  </si>
-  <si>
-    <t>Defender sees pressure from the opposing winger who is pressing and makes a calm pass to his supporting winger</t>
-  </si>
-  <si>
-    <t>17:43</t>
-  </si>
-  <si>
-    <t>Rebound (safe)</t>
-  </si>
-  <si>
-    <t>Winger battles through a mele of players to get an in close shot on the GK</t>
-  </si>
-  <si>
-    <t>GK prepared, steps off the line to make the low block</t>
-  </si>
-  <si>
-    <t>K-Barrier</t>
-  </si>
-  <si>
-    <t>22:03</t>
-  </si>
-  <si>
-    <t>23:18</t>
-  </si>
-  <si>
-    <t>Central Box</t>
-  </si>
-  <si>
-    <t>Center mid receives a ball in open play from the winger outside of the 6-yard back. Takes a low driven shot to the right.</t>
-  </si>
-  <si>
-    <t>GK standing a bit left in the goal, but is set and pushes hard through a power step and reaches to parry the ball wide for a corner.</t>
-  </si>
-  <si>
-    <t>24:34</t>
-  </si>
-  <si>
-    <t>24:47</t>
-  </si>
-  <si>
-    <t>Mid</t>
-  </si>
-  <si>
-    <t>Center mid turns after a pass outside of the 6-yard box. Dives the ball mid height to the GK right</t>
-  </si>
-  <si>
-    <t>GK is set but standing a bit too far left, is ready for the shot, parry the ball from mid height wide for a corner</t>
-  </si>
-  <si>
-    <t>25:14</t>
-  </si>
-  <si>
-    <t>Corner Left</t>
-  </si>
-  <si>
-    <t>Corner kick delivered into the GK arms</t>
-  </si>
-  <si>
-    <t>GK on the near post during the corner, set, and makes a calm save</t>
-  </si>
-  <si>
-    <t>25:15</t>
-  </si>
-  <si>
-    <t>Forward</t>
-  </si>
-  <si>
-    <t>Long drop kick bounces off an opposing player leading to our possession outside of the 6-yard box</t>
-  </si>
-  <si>
-    <t>25:42</t>
-  </si>
-  <si>
-    <t>Winger drives the ball at goal but off target</t>
-  </si>
-  <si>
-    <t>GK parry the shot going wide to be safe, resulting in a corner.</t>
-  </si>
-  <si>
-    <t>34:24</t>
-  </si>
-  <si>
-    <t>34:44</t>
-  </si>
-  <si>
-    <t>Left back cuts the ball back to switch play and ball moved up into the midfield.</t>
-  </si>
-  <si>
-    <t>37:25</t>
-  </si>
-  <si>
-    <t>Header</t>
-  </si>
-  <si>
-    <t>Header driven towards the net off a corner to the low corner</t>
-  </si>
-  <si>
-    <t>GK was moving from right to left after the corner, dives back the other way to save the ball and hold on.</t>
-  </si>
-  <si>
-    <t>37:27</t>
-  </si>
-  <si>
-    <t>37:51</t>
-  </si>
-  <si>
-    <t>Heavy</t>
-  </si>
-  <si>
-    <t>40:14</t>
-  </si>
-  <si>
-    <t>Driven</t>
-  </si>
-  <si>
-    <t>41:23</t>
-  </si>
-  <si>
-    <t>No touch, ball went to the end line and other GK got the first touch</t>
-  </si>
-  <si>
-    <t>44:05</t>
-  </si>
-  <si>
-    <t>44:28</t>
-  </si>
-  <si>
-    <t>Defender holds ball too long and kicks it off the pressing striker</t>
-  </si>
-  <si>
-    <t>Defender pressured from the winger and makes a pass out to his midfielder to push up the field</t>
-  </si>
-  <si>
-    <t>45:56</t>
-  </si>
-  <si>
-    <t>Rebound (dangerous)</t>
-  </si>
-  <si>
-    <t>Opposing midfielder drives the ball through the middle beating several players but GK blocks the ball</t>
-  </si>
-  <si>
-    <t>GK started on left post, but challenged in the middle in time to make the block and save</t>
-  </si>
-  <si>
-    <t>46:55</t>
-  </si>
-  <si>
-    <t>49:00</t>
-  </si>
-  <si>
-    <t>Unclear</t>
-  </si>
-  <si>
-    <t>Top</t>
-  </si>
-  <si>
-    <t>bouncing ball in from a cross, didn't get good enough contact</t>
-  </si>
-  <si>
-    <t>GK bobbles the bouncing ball but is able to recover.</t>
-  </si>
-  <si>
-    <t>49:02</t>
-  </si>
-  <si>
-    <t>Ball played in from the right side to center mid who takes the ball to just outside the 6-yard (on the left) and drives the ball against the grain into the GK goal left</t>
-  </si>
-  <si>
-    <t>GK tracked the player but lost the angle in goal leaving the left side of the goal open. Wasn't set and couldn't push back the opposite direction</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="6" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
     <font>
       <b/>
@@ -729,8 +731,8 @@
       <name val="Calibri"/>
     </font>
     <font>
+      <color rgb="FF333333"/>
       <sz val="11"/>
-      <color rgb="FF333333"/>
       <name val="Calibri"/>
     </font>
     <font>
@@ -740,14 +742,14 @@
     </font>
     <font>
       <b/>
+      <color rgb="FFFFFFFF"/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="Calibri"/>
     </font>
     <font>
       <i/>
+      <color rgb="FF666666"/>
       <sz val="11"/>
-      <color rgb="FF666666"/>
       <name val="Calibri"/>
     </font>
   </fonts>
@@ -800,8 +802,8 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1140,196 +1142,196 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF888888"/>
   </sheetPr>
   <dimension ref="A1:A32"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="21" x14ac:dyDescent="0.5">
+    <row r="1" ht="21" customHeight="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF666666"/>
   </sheetPr>
   <dimension ref="A1:C14"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="26" customWidth="1"/>
     <col min="2" max="2" width="36" customWidth="1"/>
     <col min="3" max="3" width="50" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
         <v>28</v>
       </c>
@@ -1340,7 +1342,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>31</v>
       </c>
@@ -1351,7 +1353,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>34</v>
       </c>
@@ -1362,7 +1364,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>37</v>
       </c>
@@ -1373,7 +1375,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>40</v>
       </c>
@@ -1381,7 +1383,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
@@ -1389,7 +1391,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>44</v>
       </c>
@@ -1400,7 +1402,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>47</v>
       </c>
@@ -1408,7 +1410,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>49</v>
       </c>
@@ -1416,7 +1418,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>51</v>
       </c>
@@ -1424,7 +1426,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>53</v>
       </c>
@@ -1432,7 +1434,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>55</v>
       </c>
@@ -1440,7 +1442,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>56</v>
       </c>
@@ -1448,41 +1450,41 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>57</v>
       </c>
       <c r="B14" t="s">
-        <v>1</v>
+        <v>58</v>
       </c>
       <c r="C14" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="B10" xr:uid="{00000000-0002-0000-0100-000000000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B10">
       <formula1>"U6,U7,U8,U9,U10,U11,U12,U13,U14,U15,U16,U17,U18,Senior"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B5" xr:uid="{00000000-0002-0000-0100-000001000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B5">
       <formula1>"Home,Away,Neutral"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="B6" xr:uid="{00000000-0002-0000-0100-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B6">
       <formula1>"Match,Friendly,Training"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFEF4444"/>
   </sheetPr>
   <dimension ref="A1:K202"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -1494,151 +1496,151 @@
     <col min="11" max="11" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H1" s="4" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I1" s="4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="J1" s="4" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="K1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>103</v>
+        <v>70</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="F2" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="G2" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="H2" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="I2" t="s">
-        <v>110</v>
+        <v>77</v>
       </c>
       <c r="J2" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
-        <v>112</v>
+        <v>79</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="D3" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="E3" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="F3" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="I3" t="s">
-        <v>115</v>
-      </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
-        <v>113</v>
+        <v>81</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="D4" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="E4" t="s">
-        <v>106</v>
+        <v>73</v>
       </c>
       <c r="F4" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="I4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
-        <v>208</v>
+        <v>83</v>
       </c>
       <c r="B5">
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>104</v>
+        <v>71</v>
       </c>
       <c r="D5" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="E5" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="F5" t="s">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="G5" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="H5" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="I5" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>117</v>
+        <v>89</v>
       </c>
       <c r="B6">
         <v>2</v>
@@ -1647,651 +1649,672 @@
         <v>37</v>
       </c>
       <c r="D6" t="s">
-        <v>105</v>
+        <v>72</v>
       </c>
       <c r="E6" t="s">
-        <v>209</v>
+        <v>84</v>
       </c>
       <c r="F6" t="s">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="G6" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="H6" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="I6" t="s">
-        <v>227</v>
+        <v>91</v>
       </c>
       <c r="J6" t="s">
-        <v>228</v>
-      </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B202" xr:uid="{00000000-0002-0000-0200-000000000000}">
+  <dataValidations count="14">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202" xr:uid="{00000000-0002-0000-0200-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B202">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C202">
       <formula1>"Us,Opponent"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202" xr:uid="{00000000-0002-0000-0200-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+      <formula1>"Us,Opponent"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
       <formula1>"Open play,Counter attack,Corner,Free kick,Penalty,Throw-in,Set piece other,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E202" xr:uid="{00000000-0002-0000-0200-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
+      <formula1>"Open play,Counter attack,Corner,Free kick,Penalty,Throw-in,Set piece other,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
       <formula1>"Header,Driven,Tap-in,Volley,Half-volley,Curled,Chip,One-v-one finish,Rebound,Deflection,Penalty,Free-kick,Own goal,Other"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F202" xr:uid="{00000000-0002-0000-0200-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
+      <formula1>"Header,Driven,Tap-in,Volley,Half-volley,Curled,Chip,One-v-one finish,Rebound,Deflection,Penalty,Free-kick,Own goal,Other"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
       <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G202" xr:uid="{00000000-0002-0000-0200-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
+      <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
       <formula1>"Top,Mid,Low,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H202" xr:uid="{00000000-0002-0000-0200-00000C000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
+      <formula1>"Top,Mid,Low,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H10:H202">
+      <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H2:H202">
       <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF10B981"/>
   </sheetPr>
   <dimension ref="A1:N202"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -2306,1116 +2329,1146 @@
     <col min="14" max="14" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>94</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="G1" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="H1" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>98</v>
+      </c>
+      <c r="J1" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="K1" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="L1" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="M1" s="4" t="s">
         <v>69</v>
-      </c>
-      <c r="D1" s="4" t="s">
-        <v>63</v>
-      </c>
-      <c r="E1" s="4" t="s">
-        <v>70</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>72</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>73</v>
-      </c>
-      <c r="I1" s="4" t="s">
-        <v>74</v>
-      </c>
-      <c r="J1" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="K1" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="L1" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="M1" s="4" t="s">
-        <v>68</v>
       </c>
       <c r="N1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="B2">
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>128</v>
+        <v>100</v>
       </c>
       <c r="D2" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="E2" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F2" t="s">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H2" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="I2" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="J2" t="s">
+        <v>75</v>
+      </c>
+      <c r="K2" t="s">
+        <v>106</v>
+      </c>
+      <c r="L2" t="s">
+        <v>107</v>
+      </c>
+      <c r="M2" t="s">
         <v>108</v>
       </c>
-      <c r="K2" t="s">
-        <v>133</v>
-      </c>
-      <c r="L2" t="s">
-        <v>134</v>
-      </c>
-      <c r="M2" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
-        <v>142</v>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" s="6" t="s">
+        <v>109</v>
       </c>
       <c r="B3">
         <v>1</v>
       </c>
       <c r="C3" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="D3" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="E3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F3" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="G3" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H3" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="I3" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="J3" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K3" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="L3" t="s">
-        <v>148</v>
+        <v>114</v>
       </c>
       <c r="M3" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" s="7" t="s">
-        <v>165</v>
+        <v>115</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" s="6" t="s">
+        <v>116</v>
       </c>
       <c r="B4">
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>166</v>
+        <v>85</v>
       </c>
       <c r="D4" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="E4" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" t="s">
+        <v>117</v>
+      </c>
+      <c r="G4" t="s">
+        <v>102</v>
+      </c>
+      <c r="H4" t="s">
+        <v>104</v>
+      </c>
+      <c r="I4" t="s">
+        <v>118</v>
+      </c>
+      <c r="J4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K4" t="s">
+        <v>76</v>
+      </c>
+      <c r="L4" t="s">
+        <v>119</v>
+      </c>
+      <c r="M4" t="s">
+        <v>120</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
         <v>121</v>
-      </c>
-      <c r="F4" t="s">
-        <v>167</v>
-      </c>
-      <c r="G4" t="s">
-        <v>121</v>
-      </c>
-      <c r="H4" t="s">
-        <v>131</v>
-      </c>
-      <c r="I4" t="s">
-        <v>168</v>
-      </c>
-      <c r="J4" t="s">
-        <v>108</v>
-      </c>
-      <c r="K4" t="s">
-        <v>109</v>
-      </c>
-      <c r="L4" t="s">
-        <v>169</v>
-      </c>
-      <c r="M4" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" s="5" t="s">
-        <v>173</v>
       </c>
       <c r="B5">
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D5" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="E5" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F5" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="G5" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H5" t="s">
-        <v>174</v>
+        <v>123</v>
       </c>
       <c r="I5" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="J5" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K5" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="L5" t="s">
-        <v>175</v>
+        <v>124</v>
       </c>
       <c r="M5" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>179</v>
+        <v>126</v>
       </c>
       <c r="B6">
         <v>1</v>
       </c>
       <c r="C6" t="s">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="D6" t="s">
+        <v>101</v>
+      </c>
+      <c r="E6" t="s">
+        <v>102</v>
+      </c>
+      <c r="F6" t="s">
+        <v>111</v>
+      </c>
+      <c r="G6" t="s">
+        <v>102</v>
+      </c>
+      <c r="H6" t="s">
+        <v>112</v>
+      </c>
+      <c r="I6" t="s">
+        <v>113</v>
+      </c>
+      <c r="J6" t="s">
+        <v>75</v>
+      </c>
+      <c r="K6" t="s">
+        <v>87</v>
+      </c>
+      <c r="L6" t="s">
+        <v>127</v>
+      </c>
+      <c r="M6" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
         <v>129</v>
-      </c>
-      <c r="E6" t="s">
-        <v>121</v>
-      </c>
-      <c r="F6" t="s">
-        <v>144</v>
-      </c>
-      <c r="G6" t="s">
-        <v>121</v>
-      </c>
-      <c r="H6" t="s">
-        <v>145</v>
-      </c>
-      <c r="I6" t="s">
-        <v>146</v>
-      </c>
-      <c r="J6" t="s">
-        <v>108</v>
-      </c>
-      <c r="K6" t="s">
-        <v>147</v>
-      </c>
-      <c r="L6" t="s">
-        <v>181</v>
-      </c>
-      <c r="M6" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" s="5" t="s">
-        <v>184</v>
       </c>
       <c r="B7">
         <v>1</v>
       </c>
       <c r="C7" t="s">
-        <v>180</v>
+        <v>90</v>
       </c>
       <c r="D7" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="E7" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F7" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="G7" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H7" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="I7" t="s">
+        <v>105</v>
+      </c>
+      <c r="J7" t="s">
+        <v>86</v>
+      </c>
+      <c r="K7" t="s">
+        <v>87</v>
+      </c>
+      <c r="L7" t="s">
+        <v>130</v>
+      </c>
+      <c r="M7" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" s="6" t="s">
         <v>132</v>
-      </c>
-      <c r="J7" t="s">
-        <v>185</v>
-      </c>
-      <c r="K7" t="s">
-        <v>147</v>
-      </c>
-      <c r="L7" t="s">
-        <v>186</v>
-      </c>
-      <c r="M7" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A8" s="7" t="s">
-        <v>188</v>
       </c>
       <c r="B8">
         <v>1</v>
       </c>
       <c r="C8" t="s">
-        <v>189</v>
+        <v>133</v>
       </c>
       <c r="D8" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="E8" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F8" t="s">
-        <v>167</v>
+        <v>117</v>
       </c>
       <c r="G8" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H8" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="I8" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="J8" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="K8" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="L8" t="s">
-        <v>190</v>
+        <v>134</v>
       </c>
       <c r="M8" t="s">
-        <v>191</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" s="7" t="s">
-        <v>195</v>
+        <v>135</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" s="6" t="s">
+        <v>136</v>
       </c>
       <c r="B9">
         <v>1</v>
       </c>
       <c r="C9" t="s">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="D9" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="E9" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F9" t="s">
-        <v>144</v>
+        <v>111</v>
       </c>
       <c r="G9" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H9" t="s">
-        <v>145</v>
+        <v>112</v>
       </c>
       <c r="I9" t="s">
-        <v>132</v>
+        <v>105</v>
       </c>
       <c r="J9" t="s">
-        <v>185</v>
+        <v>86</v>
       </c>
       <c r="K9" t="s">
-        <v>133</v>
+        <v>106</v>
       </c>
       <c r="L9" t="s">
-        <v>196</v>
+        <v>138</v>
       </c>
       <c r="M9" t="s">
-        <v>197</v>
-      </c>
-    </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A10" s="7" t="s">
-        <v>201</v>
+        <v>139</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" s="6" t="s">
+        <v>140</v>
       </c>
       <c r="B10">
         <v>2</v>
       </c>
       <c r="C10" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D10" t="s">
-        <v>202</v>
+        <v>141</v>
       </c>
       <c r="E10" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F10" t="s">
-        <v>167</v>
+        <v>117</v>
       </c>
       <c r="G10" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H10" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="I10" t="s">
-        <v>146</v>
+        <v>113</v>
       </c>
       <c r="J10" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K10" t="s">
-        <v>147</v>
+        <v>87</v>
       </c>
       <c r="L10" t="s">
-        <v>203</v>
+        <v>142</v>
       </c>
       <c r="M10" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
-        <v>216</v>
+        <v>144</v>
       </c>
       <c r="B11">
         <v>2</v>
       </c>
       <c r="C11" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D11" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="E11" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F11" t="s">
-        <v>177</v>
+        <v>122</v>
       </c>
       <c r="G11" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H11" t="s">
-        <v>217</v>
+        <v>145</v>
       </c>
       <c r="I11" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="J11" t="s">
-        <v>108</v>
+        <v>75</v>
       </c>
       <c r="K11" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="L11" t="s">
-        <v>218</v>
+        <v>146</v>
       </c>
       <c r="M11" t="s">
-        <v>219</v>
-      </c>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
-        <v>221</v>
+        <v>148</v>
       </c>
       <c r="B12">
         <v>2</v>
       </c>
       <c r="C12" t="s">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="D12" t="s">
-        <v>129</v>
+        <v>101</v>
       </c>
       <c r="E12" t="s">
-        <v>222</v>
+        <v>149</v>
       </c>
       <c r="F12" t="s">
-        <v>167</v>
+        <v>117</v>
       </c>
       <c r="G12" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="H12" t="s">
-        <v>131</v>
+        <v>104</v>
       </c>
       <c r="I12" t="s">
-        <v>168</v>
+        <v>118</v>
       </c>
       <c r="J12" t="s">
-        <v>223</v>
+        <v>150</v>
       </c>
       <c r="K12" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="L12" t="s">
-        <v>224</v>
+        <v>151</v>
       </c>
       <c r="M12" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="10">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B202" xr:uid="{00000000-0002-0000-0300-000000000000}">
+  <dataValidations count="20">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202" xr:uid="{00000000-0002-0000-0300-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B202">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C202">
       <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202" xr:uid="{00000000-0002-0000-0300-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+      <formula1>"6-Yard Box,Left Channel,Central Box,Right Channel,Wide Left,Central Distance,Wide Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
       <formula1>"Foot,Header,Deflection"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E202" xr:uid="{00000000-0002-0000-0300-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
+      <formula1>"Foot,Header,Deflection"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
       <formula1>"Yes,No,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F202" xr:uid="{00000000-0002-0000-0300-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
+      <formula1>"Yes,No,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
       <formula1>"Catch,Block,Parry,Deflect,Punch,Smother,Starfish,K-Barrier,Missed,Goal,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G202" xr:uid="{00000000-0002-0000-0300-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
+      <formula1>"Catch,Block,Parry,Deflect,Punch,Smother,Starfish,K-Barrier,Missed,Goal,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
       <formula1>"Yes,Partial,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H202" xr:uid="{00000000-0002-0000-0300-00000C000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
+      <formula1>"Yes,Partial,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H10:H202">
       <formula1>"Held,Rebound (safe),Rebound (dangerous),Corner,Out of play,Goal"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I2:I202" xr:uid="{00000000-0002-0000-0300-00000E000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H2:H202">
+      <formula1>"Held,Rebound (safe),Rebound (dangerous),Corner,Out of play,Goal"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I10:I202">
       <formula1>"A,B,C,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J2:J202" xr:uid="{00000000-0002-0000-0300-000010000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I2:I202">
+      <formula1>"A,B,C,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J10:J202">
       <formula1>"Top,Mid,Low,Unclear"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="K2:K202" xr:uid="{00000000-0002-0000-0300-000012000000}">
+    <dataValidation type="list" allowBlank="1" sqref="J2:J202">
+      <formula1>"Top,Mid,Low,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K10:K202">
+      <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="K2:K202">
       <formula1>"GK Left,Centre,GK Right,Unclear"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FF3B82F6"/>
   </sheetPr>
   <dimension ref="A1:K216"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -3430,710 +3483,710 @@
     <col min="11" max="11" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A1" s="6" t="s">
-        <v>75</v>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A2" s="6" t="s">
-        <v>76</v>
-      </c>
-      <c r="B2" s="6"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="B1" s="7"/>
+      <c r="C1" s="7"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
+      <c r="F1" s="7"/>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="B2" s="7"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="B4" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>78</v>
+        <v>156</v>
       </c>
       <c r="B5" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>79</v>
+        <v>157</v>
       </c>
       <c r="B6" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>80</v>
+        <v>158</v>
       </c>
       <c r="B7" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>81</v>
+        <v>159</v>
       </c>
       <c r="B8" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>82</v>
+        <v>160</v>
       </c>
       <c r="B9" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>83</v>
+        <v>161</v>
       </c>
       <c r="B10" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>84</v>
+        <v>162</v>
       </c>
       <c r="B11" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
-        <v>85</v>
+        <v>163</v>
       </c>
       <c r="B12" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
-        <v>86</v>
+        <v>164</v>
       </c>
       <c r="B13" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B16" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>87</v>
+        <v>165</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>88</v>
+        <v>166</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="F16" s="4" t="s">
-        <v>90</v>
+        <v>168</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>91</v>
+        <v>169</v>
       </c>
       <c r="H16" s="4" t="s">
-        <v>92</v>
+        <v>170</v>
       </c>
       <c r="I16" s="4" t="s">
-        <v>93</v>
+        <v>171</v>
       </c>
       <c r="J16" s="4" t="s">
-        <v>94</v>
+        <v>172</v>
       </c>
       <c r="K16" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
-        <v>118</v>
+        <v>173</v>
       </c>
       <c r="B17">
         <v>1</v>
       </c>
       <c r="C17" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="D17" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E17" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F17" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G17" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H17" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="I17" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="K17" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
-        <v>136</v>
+        <v>180</v>
       </c>
       <c r="B18">
         <v>1</v>
       </c>
       <c r="C18" t="s">
-        <v>137</v>
+        <v>181</v>
       </c>
       <c r="D18" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="E18" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F18" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="G18" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H18" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I18" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="J18" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="K18" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
-        <v>150</v>
+        <v>186</v>
       </c>
       <c r="B19">
         <v>1</v>
       </c>
       <c r="C19" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="D19" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="E19" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F19" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G19" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="H19" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="I19" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="K19" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
-        <v>157</v>
+        <v>192</v>
       </c>
       <c r="B20">
         <v>1</v>
       </c>
       <c r="C20" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="D20" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E20" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="F20" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G20" t="s">
-        <v>159</v>
+        <v>194</v>
       </c>
       <c r="H20" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I20" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="J20" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="K20" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+        <v>196</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
-        <v>161</v>
+        <v>197</v>
       </c>
       <c r="B21">
         <v>1</v>
       </c>
       <c r="C21" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="E21" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F21" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G21" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="H21" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="I21" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="J21" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="K21" t="s">
-        <v>162</v>
-      </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
-        <v>163</v>
+        <v>199</v>
       </c>
       <c r="B22">
         <v>1</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="D22" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E22" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F22" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G22" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H22" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="I22" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="J22" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="K22" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
-        <v>171</v>
+        <v>201</v>
       </c>
       <c r="B23">
         <v>1</v>
       </c>
       <c r="C23" t="s">
+        <v>181</v>
+      </c>
+      <c r="D23" t="s">
+        <v>182</v>
+      </c>
+      <c r="E23" t="s">
+        <v>102</v>
+      </c>
+      <c r="F23" t="s">
         <v>137</v>
       </c>
-      <c r="D23" t="s">
-        <v>138</v>
-      </c>
-      <c r="E23" t="s">
-        <v>121</v>
-      </c>
-      <c r="F23" t="s">
-        <v>122</v>
-      </c>
       <c r="G23" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H23" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I23" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="J23" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="K23" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
-        <v>178</v>
+        <v>203</v>
       </c>
       <c r="B24">
         <v>1</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="D24" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E24" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F24" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G24" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H24" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I24" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="J24" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
-        <v>183</v>
+        <v>204</v>
       </c>
       <c r="B25">
         <v>1</v>
       </c>
       <c r="C25" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="D25" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E25" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F25" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G25" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H25" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I25" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
-        <v>192</v>
+        <v>205</v>
       </c>
       <c r="B26">
         <v>1</v>
       </c>
       <c r="C26" t="s">
+        <v>181</v>
+      </c>
+      <c r="D26" t="s">
+        <v>188</v>
+      </c>
+      <c r="E26" t="s">
+        <v>102</v>
+      </c>
+      <c r="F26" t="s">
         <v>137</v>
       </c>
-      <c r="D26" t="s">
-        <v>152</v>
-      </c>
-      <c r="E26" t="s">
-        <v>121</v>
-      </c>
-      <c r="F26" t="s">
-        <v>122</v>
-      </c>
       <c r="G26" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="H26" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="I26" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="J26" t="s">
-        <v>155</v>
+        <v>195</v>
       </c>
       <c r="K26" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
-        <v>198</v>
+        <v>208</v>
       </c>
       <c r="B27">
         <v>2</v>
       </c>
       <c r="C27" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="D27" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E27" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F27" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G27" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H27" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="I27" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="J27" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
-        <v>199</v>
+        <v>209</v>
       </c>
       <c r="B28">
         <v>2</v>
       </c>
       <c r="C28" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="D28" t="s">
-        <v>138</v>
+        <v>182</v>
       </c>
       <c r="E28" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F28" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="G28" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H28" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I28" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="J28" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="K28" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B29">
         <v>2</v>
       </c>
       <c r="C29" t="s">
+        <v>181</v>
+      </c>
+      <c r="D29" t="s">
+        <v>182</v>
+      </c>
+      <c r="E29" t="s">
+        <v>102</v>
+      </c>
+      <c r="F29" t="s">
         <v>137</v>
       </c>
-      <c r="D29" t="s">
-        <v>138</v>
-      </c>
-      <c r="E29" t="s">
-        <v>121</v>
-      </c>
-      <c r="F29" t="s">
-        <v>122</v>
-      </c>
       <c r="G29" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H29" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I29" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="J29" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="B30">
         <v>2</v>
       </c>
       <c r="C30" t="s">
-        <v>158</v>
+        <v>193</v>
       </c>
       <c r="D30" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E30" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F30" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="G30" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H30" t="s">
-        <v>109</v>
+        <v>76</v>
       </c>
       <c r="I30" t="s">
-        <v>154</v>
+        <v>190</v>
       </c>
       <c r="J30" t="s">
-        <v>207</v>
-      </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="B31">
         <v>2</v>
       </c>
       <c r="C31" t="s">
-        <v>151</v>
+        <v>187</v>
       </c>
       <c r="D31" t="s">
-        <v>152</v>
+        <v>188</v>
       </c>
       <c r="E31" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F31" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G31" t="s">
-        <v>153</v>
+        <v>189</v>
       </c>
       <c r="H31" t="s">
-        <v>124</v>
+        <v>177</v>
       </c>
       <c r="I31" t="s">
-        <v>193</v>
+        <v>206</v>
       </c>
       <c r="K31" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B32">
         <v>2</v>
       </c>
       <c r="C32" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="D32" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E32" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F32" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G32" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H32" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I32" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="J32" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="K32" t="s">
-        <v>214</v>
-      </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+        <v>217</v>
+      </c>
+    </row>
+    <row r="33" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
       <c r="B33">
         <v>2</v>
       </c>
       <c r="C33" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="D33" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E33" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F33" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G33" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H33" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I33" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="J33" t="s">
-        <v>140</v>
+        <v>184</v>
       </c>
       <c r="K33" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>220</v>
       </c>
@@ -4141,600 +4194,600 @@
         <v>2</v>
       </c>
       <c r="C34" t="s">
-        <v>119</v>
+        <v>174</v>
       </c>
       <c r="D34" t="s">
-        <v>120</v>
+        <v>175</v>
       </c>
       <c r="E34" t="s">
-        <v>121</v>
+        <v>102</v>
       </c>
       <c r="F34" t="s">
-        <v>122</v>
+        <v>137</v>
       </c>
       <c r="G34" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H34" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I34" t="s">
-        <v>125</v>
+        <v>178</v>
       </c>
       <c r="J34" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
-        <v>226</v>
+        <v>221</v>
       </c>
       <c r="B35">
         <v>2</v>
       </c>
       <c r="C35" t="s">
+        <v>181</v>
+      </c>
+      <c r="D35" t="s">
+        <v>182</v>
+      </c>
+      <c r="E35" t="s">
+        <v>102</v>
+      </c>
+      <c r="F35" t="s">
         <v>137</v>
       </c>
-      <c r="D35" t="s">
-        <v>138</v>
-      </c>
-      <c r="E35" t="s">
-        <v>121</v>
-      </c>
-      <c r="F35" t="s">
-        <v>122</v>
-      </c>
       <c r="G35" t="s">
-        <v>123</v>
+        <v>176</v>
       </c>
       <c r="H35" t="s">
-        <v>139</v>
+        <v>183</v>
       </c>
       <c r="I35" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
-    <row r="203" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A203" s="5"/>
     </row>
-    <row r="204" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A204" s="5"/>
     </row>
-    <row r="205" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A205" s="5"/>
     </row>
-    <row r="206" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A206" s="5"/>
     </row>
-    <row r="207" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A207" s="5"/>
     </row>
-    <row r="208" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A208" s="5"/>
     </row>
-    <row r="209" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A209" s="5"/>
     </row>
-    <row r="210" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A210" s="5"/>
     </row>
-    <row r="211" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A211" s="5"/>
     </row>
-    <row r="212" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A212" s="5"/>
     </row>
-    <row r="213" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A213" s="5"/>
     </row>
-    <row r="214" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A214" s="5"/>
     </row>
-    <row r="215" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A215" s="5"/>
     </row>
-    <row r="216" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A216" s="5"/>
     </row>
   </sheetData>
@@ -4742,44 +4795,68 @@
     <mergeCell ref="A1:F1"/>
     <mergeCell ref="A2:F2"/>
   </mergeCells>
-  <dataValidations count="8">
-    <dataValidation type="list" allowBlank="1" sqref="B17:B216" xr:uid="{00000000-0002-0000-0400-000000000000}">
+  <dataValidations count="16">
+    <dataValidation type="list" allowBlank="1" sqref="B100:B216">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C17:C216" xr:uid="{00000000-0002-0000-0400-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B17:B216">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C100:C216">
       <formula1>"Goal kick,After save,Backpass,Loose ball in box,Throw-in to GK,Free kick to GK"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D17:D216" xr:uid="{00000000-0002-0000-0400-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C17:C216">
+      <formula1>"Goal kick,After save,Backpass,Loose ball in box,Throw-in to GK,Free kick to GK"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D100:D216">
       <formula1>"GK Short Kick,GK Long Kick,Throw,Pass,Drop-kick"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E17:F216" xr:uid="{00000000-0002-0000-0400-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D17:D216">
+      <formula1>"GK Short Kick,GK Long Kick,Throw,Pass,Drop-kick"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E100:F216">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G17:G216" xr:uid="{00000000-0002-0000-0400-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E17:F216">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G100:G216">
       <formula1>"Short to defender,Sideways across back,Long to forward,Switch wide,Backwards under pressure,Clearance under pressure,Drilled into channel"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H17:H216" xr:uid="{00000000-0002-0000-0400-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G17:G216">
+      <formula1>"Short to defender,Sideways across back,Long to forward,Switch wide,Backwards under pressure,Clearance under pressure,Drilled into channel"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H100:H216">
       <formula1>"Left,Centre,Right,Backwards"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="I17:I216" xr:uid="{00000000-0002-0000-0400-00000C000000}">
+    <dataValidation type="list" allowBlank="1" sqref="H17:H216">
+      <formula1>"Left,Centre,Right,Backwards"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="I100:I216">
       <formula1>"Defender,Midfielder,Forward,Out of play,Opponent (turnover)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="J17:J216" xr:uid="{00000000-0002-0000-0400-00000E000000}">
+    <dataValidation type="list" allowBlank="1" sqref="I17:I216">
+      <formula1>"Defender,Midfielder,Forward,Out of play,Opponent (turnover)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J100:J216">
+      <formula1>"Clean,Heavy,Two touches,Mishit"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="J17:J216">
       <formula1>"Clean,Heavy,Two touches,Mishit"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFF97316"/>
   </sheetPr>
   <dimension ref="A1:I202"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -4790,674 +4867,695 @@
     <col min="9" max="9" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="4" t="s">
+        <v>222</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>223</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>224</v>
+      </c>
+      <c r="F1" s="4" t="s">
         <v>95</v>
       </c>
-      <c r="D1" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="E1" s="4" t="s">
+      <c r="G1" s="4" t="s">
+        <v>225</v>
+      </c>
+      <c r="H1" s="4" t="s">
         <v>97</v>
-      </c>
-      <c r="F1" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="G1" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="H1" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="I1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B202" xr:uid="{00000000-0002-0000-0500-000000000000}">
+  <dataValidations count="14">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202" xr:uid="{00000000-0002-0000-0500-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B202">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C202">
       <formula1>"Left,Right,Corner Left,Corner Right"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202" xr:uid="{00000000-0002-0000-0500-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+      <formula1>"Left,Right,Corner Left,Corner Right"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
       <formula1>"Whipped,Floated,Driven,Cut-back,Looped"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E202" xr:uid="{00000000-0002-0000-0500-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
+      <formula1>"Whipped,Floated,Driven,Cut-back,Looped"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
       <formula1>"Near post,6yd,Penalty spot,Far post,Out of box"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F202" xr:uid="{00000000-0002-0000-0500-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
+      <formula1>"Near post,6yd,Penalty spot,Far post,Out of box"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
       <formula1>"Catch,Punch,Tip-over,Stayed on line,Missed/Misjudged,Defender cleared"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G202" xr:uid="{00000000-0002-0000-0500-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
+      <formula1>"Catch,Punch,Tip-over,Stayed on line,Missed/Misjudged,Defender cleared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
       <formula1>"On line,Edge of 6yd,Edge of 18yd,Outside box"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="H2:H202" xr:uid="{00000000-0002-0000-0500-00000C000000}">
+    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
+      <formula1>"On line,Edge of 6yd,Edge of 18yd,Outside box"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H10:H202">
+      <formula1>"Held,Punched away,Tipped over,Conceded,Cleared by defender,Shot from rebound"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="H2:H202">
       <formula1>"Held,Punched away,Tipped over,Conceded,Cleared by defender,Shot from rebound"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFA78BFA"/>
   </sheetPr>
   <dimension ref="A1:H202"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -5469,668 +5567,686 @@
     <col min="8" max="8" width="40" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>99</v>
+        <v>226</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>100</v>
+        <v>227</v>
       </c>
       <c r="E1" s="4" t="s">
-        <v>89</v>
+        <v>167</v>
       </c>
       <c r="F1" s="4" t="s">
-        <v>101</v>
+        <v>228</v>
       </c>
       <c r="G1" s="4" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="H1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B202" xr:uid="{00000000-0002-0000-0600-000000000000}">
+  <dataValidations count="12">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202" xr:uid="{00000000-0002-0000-0600-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B202">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C202">
       <formula1>"Clearance,Interception,Tackle,Header"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202" xr:uid="{00000000-0002-0000-0600-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+      <formula1>"Clearance,Interception,Tackle,Header"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
       <formula1>"In box,Edge of box,5–15 yards out,15+ yards out"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="E2:E202" xr:uid="{00000000-0002-0000-0600-000006000000}">
+    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
+      <formula1>"In box,Edge of box,5–15 yards out,15+ yards out"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="E10:E202">
       <formula1>"Yes,No"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="F2:F202" xr:uid="{00000000-0002-0000-0600-000008000000}">
+    <dataValidation type="list" allowBlank="1" sqref="E2:E202">
+      <formula1>"Yes,No"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="F10:F202">
       <formula1>"None,1 attacker,2+ attackers"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="G2:G202" xr:uid="{00000000-0002-0000-0600-00000A000000}">
+    <dataValidation type="list" allowBlank="1" sqref="F2:F202">
+      <formula1>"None,1 attacker,2+ attackers"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G10:G202">
+      <formula1>"Possession retained,Cleared safely,Conceded turnover,Goal conceded"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="G2:G202">
       <formula1>"Possession retained,Cleared safely,Conceded turnover,Goal conceded"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr>
     <tabColor rgb="FFD4A853"/>
   </sheetPr>
   <dimension ref="A1:E202"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.35" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="12" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
@@ -6139,639 +6255,648 @@
     <col min="5" max="5" width="70" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>102</v>
+        <v>229</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>73</v>
+        <v>97</v>
       </c>
       <c r="E1" s="4" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5"/>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5"/>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5"/>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5"/>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5"/>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5"/>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
-    <row r="50" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A50" s="5"/>
     </row>
-    <row r="51" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A51" s="5"/>
     </row>
-    <row r="52" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A52" s="5"/>
     </row>
-    <row r="53" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A53" s="5"/>
     </row>
-    <row r="54" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A54" s="5"/>
     </row>
-    <row r="55" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A55" s="5"/>
     </row>
-    <row r="56" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A56" s="5"/>
     </row>
-    <row r="57" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A57" s="5"/>
     </row>
-    <row r="58" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A58" s="5"/>
     </row>
-    <row r="59" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A59" s="5"/>
     </row>
-    <row r="60" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A60" s="5"/>
     </row>
-    <row r="61" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A61" s="5"/>
     </row>
-    <row r="62" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A62" s="5"/>
     </row>
-    <row r="63" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A63" s="5"/>
     </row>
-    <row r="64" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A64" s="5"/>
     </row>
-    <row r="65" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A65" s="5"/>
     </row>
-    <row r="66" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A66" s="5"/>
     </row>
-    <row r="67" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A67" s="5"/>
     </row>
-    <row r="68" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A68" s="5"/>
     </row>
-    <row r="69" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A69" s="5"/>
     </row>
-    <row r="70" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A70" s="5"/>
     </row>
-    <row r="71" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A71" s="5"/>
     </row>
-    <row r="72" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A72" s="5"/>
     </row>
-    <row r="73" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A73" s="5"/>
     </row>
-    <row r="74" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A74" s="5"/>
     </row>
-    <row r="75" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A75" s="5"/>
     </row>
-    <row r="76" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A76" s="5"/>
     </row>
-    <row r="77" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A77" s="5"/>
     </row>
-    <row r="78" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A78" s="5"/>
     </row>
-    <row r="79" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A79" s="5"/>
     </row>
-    <row r="80" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A80" s="5"/>
     </row>
-    <row r="81" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A81" s="5"/>
     </row>
-    <row r="82" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A82" s="5"/>
     </row>
-    <row r="83" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A83" s="5"/>
     </row>
-    <row r="84" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A84" s="5"/>
     </row>
-    <row r="85" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A85" s="5"/>
     </row>
-    <row r="86" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A86" s="5"/>
     </row>
-    <row r="87" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A87" s="5"/>
     </row>
-    <row r="88" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A88" s="5"/>
     </row>
-    <row r="89" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A89" s="5"/>
     </row>
-    <row r="90" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A90" s="5"/>
     </row>
-    <row r="91" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A91" s="5"/>
     </row>
-    <row r="92" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A92" s="5"/>
     </row>
-    <row r="93" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A93" s="5"/>
     </row>
-    <row r="94" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A94" s="5"/>
     </row>
-    <row r="95" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A95" s="5"/>
     </row>
-    <row r="96" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A96" s="5"/>
     </row>
-    <row r="97" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A97" s="5"/>
     </row>
-    <row r="98" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A98" s="5"/>
     </row>
-    <row r="99" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A99" s="5"/>
     </row>
-    <row r="100" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A100" s="5"/>
     </row>
-    <row r="101" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A101" s="5"/>
     </row>
-    <row r="102" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A102" s="5"/>
     </row>
-    <row r="103" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A103" s="5"/>
     </row>
-    <row r="104" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A104" s="5"/>
     </row>
-    <row r="105" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A105" s="5"/>
     </row>
-    <row r="106" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A106" s="5"/>
     </row>
-    <row r="107" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A107" s="5"/>
     </row>
-    <row r="108" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A108" s="5"/>
     </row>
-    <row r="109" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A109" s="5"/>
     </row>
-    <row r="110" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A110" s="5"/>
     </row>
-    <row r="111" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A111" s="5"/>
     </row>
-    <row r="112" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A112" s="5"/>
     </row>
-    <row r="113" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A113" s="5"/>
     </row>
-    <row r="114" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A114" s="5"/>
     </row>
-    <row r="115" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A115" s="5"/>
     </row>
-    <row r="116" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A116" s="5"/>
     </row>
-    <row r="117" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A117" s="5"/>
     </row>
-    <row r="118" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A118" s="5"/>
     </row>
-    <row r="119" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A119" s="5"/>
     </row>
-    <row r="120" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A120" s="5"/>
     </row>
-    <row r="121" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A121" s="5"/>
     </row>
-    <row r="122" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A122" s="5"/>
     </row>
-    <row r="123" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A123" s="5"/>
     </row>
-    <row r="124" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A124" s="5"/>
     </row>
-    <row r="125" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A125" s="5"/>
     </row>
-    <row r="126" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A126" s="5"/>
     </row>
-    <row r="127" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A127" s="5"/>
     </row>
-    <row r="128" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A128" s="5"/>
     </row>
-    <row r="129" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A129" s="5"/>
     </row>
-    <row r="130" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A130" s="5"/>
     </row>
-    <row r="131" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A131" s="5"/>
     </row>
-    <row r="132" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A132" s="5"/>
     </row>
-    <row r="133" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A133" s="5"/>
     </row>
-    <row r="134" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A134" s="5"/>
     </row>
-    <row r="135" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A135" s="5"/>
     </row>
-    <row r="136" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A136" s="5"/>
     </row>
-    <row r="137" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A137" s="5"/>
     </row>
-    <row r="138" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A138" s="5"/>
     </row>
-    <row r="139" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A139" s="5"/>
     </row>
-    <row r="140" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A140" s="5"/>
     </row>
-    <row r="141" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A141" s="5"/>
     </row>
-    <row r="142" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A142" s="5"/>
     </row>
-    <row r="143" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A143" s="5"/>
     </row>
-    <row r="144" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A144" s="5"/>
     </row>
-    <row r="145" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A145" s="5"/>
     </row>
-    <row r="146" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A146" s="5"/>
     </row>
-    <row r="147" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A147" s="5"/>
     </row>
-    <row r="148" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A148" s="5"/>
     </row>
-    <row r="149" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A149" s="5"/>
     </row>
-    <row r="150" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A150" s="5"/>
     </row>
-    <row r="151" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A151" s="5"/>
     </row>
-    <row r="152" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A152" s="5"/>
     </row>
-    <row r="153" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A153" s="5"/>
     </row>
-    <row r="154" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A154" s="5"/>
     </row>
-    <row r="155" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A155" s="5"/>
     </row>
-    <row r="156" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A156" s="5"/>
     </row>
-    <row r="157" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A157" s="5"/>
     </row>
-    <row r="158" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A158" s="5"/>
     </row>
-    <row r="159" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A159" s="5"/>
     </row>
-    <row r="160" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A160" s="5"/>
     </row>
-    <row r="161" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A161" s="5"/>
     </row>
-    <row r="162" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A162" s="5"/>
     </row>
-    <row r="163" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A163" s="5"/>
     </row>
-    <row r="164" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A164" s="5"/>
     </row>
-    <row r="165" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A165" s="5"/>
     </row>
-    <row r="166" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A166" s="5"/>
     </row>
-    <row r="167" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A167" s="5"/>
     </row>
-    <row r="168" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A168" s="5"/>
     </row>
-    <row r="169" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A169" s="5"/>
     </row>
-    <row r="170" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A170" s="5"/>
     </row>
-    <row r="171" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A171" s="5"/>
     </row>
-    <row r="172" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A172" s="5"/>
     </row>
-    <row r="173" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A173" s="5"/>
     </row>
-    <row r="174" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A174" s="5"/>
     </row>
-    <row r="175" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A175" s="5"/>
     </row>
-    <row r="176" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A176" s="5"/>
     </row>
-    <row r="177" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A177" s="5"/>
     </row>
-    <row r="178" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A178" s="5"/>
     </row>
-    <row r="179" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A179" s="5"/>
     </row>
-    <row r="180" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A180" s="5"/>
     </row>
-    <row r="181" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A181" s="5"/>
     </row>
-    <row r="182" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A182" s="5"/>
     </row>
-    <row r="183" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A183" s="5"/>
     </row>
-    <row r="184" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A184" s="5"/>
     </row>
-    <row r="185" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A185" s="5"/>
     </row>
-    <row r="186" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A186" s="5"/>
     </row>
-    <row r="187" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A187" s="5"/>
     </row>
-    <row r="188" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A188" s="5"/>
     </row>
-    <row r="189" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A189" s="5"/>
     </row>
-    <row r="190" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A190" s="5"/>
     </row>
-    <row r="191" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A191" s="5"/>
     </row>
-    <row r="192" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A192" s="5"/>
     </row>
-    <row r="193" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A193" s="5"/>
     </row>
-    <row r="194" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A194" s="5"/>
     </row>
-    <row r="195" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A195" s="5"/>
     </row>
-    <row r="196" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A196" s="5"/>
     </row>
-    <row r="197" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A197" s="5"/>
     </row>
-    <row r="198" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A198" s="5"/>
     </row>
-    <row r="199" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A199" s="5"/>
     </row>
-    <row r="200" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A200" s="5"/>
     </row>
-    <row r="201" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A201" s="5"/>
     </row>
-    <row r="202" spans="1:1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A202" s="5"/>
     </row>
   </sheetData>
-  <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" sqref="B2:B202" xr:uid="{00000000-0002-0000-0700-000000000000}">
+  <dataValidations count="6">
+    <dataValidation type="list" allowBlank="1" sqref="B10:B202">
       <formula1>"1,2"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="C2:C202" xr:uid="{00000000-0002-0000-0700-000002000000}">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B202">
+      <formula1>"1,2"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="C10:C202">
       <formula1>"1v1 faced,Recovery save,Error leading to goal,Big moment (other)"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" sqref="D2:D202" xr:uid="{00000000-0002-0000-0700-000004000000}">
+    <dataValidation type="list" allowBlank="1" sqref="C2:C202">
+      <formula1>"1v1 faced,Recovery save,Error leading to goal,Big moment (other)"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D10:D202">
+      <formula1>"Won,Conceded,Saved,Cleared"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" sqref="D2:D202">
       <formula1>"Won,Conceded,Saved,Cleared"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>